--- a/data/rubble-registry/dumps.xlsx
+++ b/data/rubble-registry/dumps.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -440,7 +440,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -482,10 +482,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>متوسط ارتفاع الأنقاض (م)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>الجهة المشغّلة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
